--- a/data/trans_dic/P1401-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1401-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,86</t>
+          <t>0,98; 2,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,97</t>
+          <t>1,03; 2,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,56</t>
+          <t>1,86; 4,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,97</t>
+          <t>1,95; 3,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,19</t>
+          <t>1,97; 4,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,44</t>
+          <t>3,37; 5,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,21</t>
+          <t>1,83; 3,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,22</t>
+          <t>1,7; 3,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,07; 4,68</t>
+          <t>3,08; 4,57</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,56</t>
+          <t>0,64; 1,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,07</t>
+          <t>0,35; 1,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,23</t>
+          <t>1,28; 2,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,47</t>
+          <t>1,14; 2,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,9</t>
+          <t>0,85; 1,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,11</t>
+          <t>1,39; 2,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,76</t>
+          <t>0,92; 1,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,3</t>
+          <t>0,69; 1,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,01</t>
+          <t>1,47; 2,14</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -903,42 +903,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,36</t>
+          <t>0,13; 1,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,76</t>
+          <t>1,74; 4,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,34</t>
+          <t>0,23; 2,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,28</t>
+          <t>1,98; 5,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,33</t>
+          <t>0,81; 2,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,43</t>
+          <t>0,32; 1,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,81</t>
+          <t>1,17; 2,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,72</t>
+          <t>1,43; 2,77</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -1008,32 +1008,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,59</t>
+          <t>0,81; 1,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,26</t>
+          <t>0,63; 1,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,46</t>
+          <t>1,75; 2,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,53</t>
+          <t>1,53; 2,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,56</t>
+          <t>1,58; 2,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,55</t>
+          <t>1,92; 2,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,77</t>
+          <t>1,17; 1,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,45</t>
+          <t>1,93; 2,5</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16060</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32407</t>
+          <t>35348</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48467</t>
+          <t>52247</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10306; 27906</t>
+          <t>9596; 28213</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8106; 22421</t>
+          <t>7755; 22196</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10416; 23374</t>
+          <t>10696; 24309</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27033; 53130</t>
+          <t>26097; 51119</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17850; 41633</t>
+          <t>19560; 42742</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25396; 40911</t>
+          <t>27598; 44434</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41985; 74246</t>
+          <t>42303; 74269</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29836; 56350</t>
+          <t>29664; 57329</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>38837; 59192</t>
+          <t>42971; 63836</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36733</t>
+          <t>39007</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36133</t>
+          <t>38821</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>72866</t>
+          <t>77828</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11949; 30610</t>
+          <t>12516; 31046</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7309; 22186</t>
+          <t>7322; 22382</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25033; 51025</t>
+          <t>28482; 52552</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19055; 43291</t>
+          <t>19973; 43123</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17346; 37790</t>
+          <t>16995; 38792</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25676; 47115</t>
+          <t>30185; 49765</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34617; 65359</t>
+          <t>34184; 64189</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26758; 52833</t>
+          <t>27910; 54391</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56386; 90836</t>
+          <t>64584; 94120</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16084</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9400</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>29250</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7420</t>
+          <t>0; 7424</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>734; 7415</t>
+          <t>735; 7737</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9942; 24288</t>
+          <t>12376; 28752</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1057; 10750</t>
+          <t>1046; 10597</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10959; 28974</t>
+          <t>10891; 29046</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5640; 15391</t>
+          <t>5970; 16482</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2342; 13402</t>
+          <t>2983; 14032</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11989; 30833</t>
+          <t>12857; 30063</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17830; 35580</t>
+          <t>20695; 40033</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68877</t>
+          <t>74507</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77940</t>
+          <t>84818</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>146817</t>
+          <t>159325</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26976; 54219</t>
+          <t>27595; 53446</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20897; 42442</t>
+          <t>21179; 43194</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52018; 84801</t>
+          <t>61422; 91712</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55179; 89869</t>
+          <t>54431; 90370</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54630; 90563</t>
+          <t>55649; 92782</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>62045; 92996</t>
+          <t>71320; 98026</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>91672; 134614</t>
+          <t>92212; 134728</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>84047; 122599</t>
+          <t>80741; 123218</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>125037; 173663</t>
+          <t>139789; 181133</t>
         </is>
       </c>
     </row>
